--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/4148-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/4148-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{668CE72E-9BCC-45AA-AC7B-3E29835F41FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD454CB6-882E-47F0-98E6-8F78FA120A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{F11CE774-042E-47E1-B05F-8A92BC3CAA66}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{C5AA0CD4-C759-4756-B0AA-C7F3C9C5CB94}"/>
   </bookViews>
   <sheets>
     <sheet name="4148-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1478,20 +1478,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B9B73E7-26AD-42D6-BC3E-DA678AF9CDA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F273BFA-CCA9-4FE2-B779-737CB2EA3382}">
   <dimension ref="A1:R29"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.21875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1519,7 +1519,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1549,7 +1549,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1645,7 +1645,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1755,7 +1755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2025</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="37">
         <v>2024</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="39">
         <v>2023</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>26</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>26</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="37">
         <v>2022</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>26</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2021</v>
       </c>
@@ -2529,7 +2529,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>26</v>
       </c>
@@ -2641,7 +2641,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2020</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>26</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>2019</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>2018</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>2017</v>
       </c>
@@ -2969,7 +2969,7 @@
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="37" t="s">
         <v>45</v>
       </c>
